--- a/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du goûter. Alice sent le cacao. Maman appelle. Alice va à la table. Elle pose les fesses sur la chaise. Elle est assise. Maman s'assoit près d'elle. Elles sont ensemble. Le bol est chaud. Alice mange assise. La cuillère cliquette. Maman dit : on mange ensemble, à table. Alice reste assise. Elle croque le biscuit. Il est croustillant. Maman sourit. Alice sourit aussi. Elles restent ensemble à table.</t>
+          <t>C'est l'heure du goûter. Alice sent le cacao. Maman appelle. Alice va à la table. Elle pose les fesses sur la chaise. Elle est assise. Maman s'assoit près d'elle. Elles sont ensemble. Le bol est chaud. Alice mange assise. La cuillère cliquette. On mange ensemble, à table. Alice reste assise. Elle croque le biscuit. Il est croustillant. Maman sourit. Alice sourit aussi. Elles restent ensemble à table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est l'heure du goûter. Alice sent le cacao. Maman appelle. Alice va à la table. Elle pose les fesses sur la chaise. Elle est assise. Maman s'assoit près d'elle. Elles sont ensemble. Le bol est chaud. Alice mange assise. La cuillère cliquette.
+maman|On mange ensemble, à table.
+narrateur|Alice reste assise. Elle croque le biscuit. Il est croustillant. Maman sourit. Alice sourit aussi. Elles restent ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Alice va goûter. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Alice est assise. Les fesses sont sur la chaise. Maman et Alice mangent ensemble, à table.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Alice boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Alice reste assise. Elle croque le biscuit. Il est croustillant. Maman sourit. Alice sourit aussi. Elles restent ensemble à table.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Alice va goûter. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Alice est assise. Les fesses sont sur la chaise. Maman et Alice mangent ensemble, à table.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Alice boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alice s'assoit pour le goûter</t>
+          <t>Le rayon couché</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un rayon couché s'étire sur le plancher. L'horloge fait tic. Le cacao fume. Amir s'assoit. Il croque le biscuit, à table, avec maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du goûter. Alice sent le cacao. Maman appelle. Alice va à la table. Elle pose les fesses sur la chaise. Elle est assise. Maman s'assoit près d'elle. Elles sont ensemble. Le bol est chaud. Alice mange assise. La cuillère cliquette. On mange ensemble, à table. Alice reste assise. Elle croque le biscuit. Il est croustillant. Maman sourit. Alice sourit aussi. Elles restent ensemble à table.</t>
+          <t>Un rayon couché s'étire sur le plancher. Il est long, tout doré. L'horloge fait tic, tic. Le salon est calme, derrière. Ça sent le cacao. Une petite fumée sort du bol. La boîte des biscuits est sur la table. Elle est ronde, un peu rouge. Amir vit ici, avec maman. Papa est au jardin, tout près. Une mouche tapote la vitre. Tic. Tic. Amir arrive du salon. Ses chaussettes glissent un peu. Elles sont rouges, tout douces. Maman, ça sent le chocolat ! Oui, Amir. C'est l'heure du goûter. Viens t'asseoir. Amir va vers sa chaise. Le bois du plancher est chaud. Tu as vu le rayon couché ? Il est long. Il tire un peu la chaise. Il s'assoit. Il pose les pieds par terre. Bravo, Amir. Tu es bien assis. Maman s'assoit près de lui. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Il pose les mains. Le bol est chaud. La cuillère cliquette. Tu as vu la petite fumée ? Elle fait des ronds. On attend un petit moment. Amir tient sa cuillère. Il reste assis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1329,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est l'heure du goûter. Alice sent le cacao. Maman appelle. Alice va à la table. Elle pose les fesses sur la chaise. Elle est assise. Maman s'assoit près d'elle. Elles sont ensemble. Le bol est chaud. Alice mange assise. La cuillère cliquette.
-maman|On mange ensemble, à table.
-narrateur|Alice reste assise. Elle croque le biscuit. Il est croustillant. Maman sourit. Alice sourit aussi. Elles restent ensemble à table.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un rayon couché s'étire sur le plancher.
+narrateur|Il est long, tout doré.
+narrateur|L'horloge fait tic, tic.
+narrateur|Le salon est calme, derrière.
+narrateur|Ça sent le cacao.
+narrateur|Une petite fumée sort du bol.
+narrateur|La boîte des biscuits est sur la table.
+narrateur|Elle est ronde, un peu rouge.
+narrateur|Amir vit ici, avec maman.
+narrateur|Papa est au jardin, tout près.
+narrateur|Une mouche tapote la vitre.
+narrateur|Tic. Tic.
+narrateur|Amir arrive du salon.
+narrateur|Ses chaussettes glissent un peu.
+narrateur|Elles sont rouges, tout douces.
+enfant-m|Maman, ça sent le chocolat !
+maman|Oui, Amir.
+maman|C'est l'heure du goûter.
+maman|Viens t'asseoir.
+narrateur|Amir va vers sa chaise.
+narrateur|Le bois du plancher est chaud.
+maman|Tu as vu le rayon couché ?
+enfant-m|Il est long.
+narrateur|Il tire un peu la chaise.
+narrateur|Il s'assoit.
+narrateur|Il pose les pieds par terre.
+maman|Bravo, Amir.
+maman|Tu es bien assis.
+narrateur|Maman s'assoit près de lui.
+maman|On est ensemble.
+maman|On mange à table.
+narrateur|Sa chaise ne bouge plus.
+maman|Tu poses les mains sur la table ?
+narrateur|Il pose les mains.
+narrateur|Le bol est chaud.
+narrateur|La cuillère cliquette.
+maman|Tu as vu la petite fumée ?
+enfant-m|Elle fait des ronds.
+maman|On attend un petit moment.
+narrateur|Amir tient sa cuillère.
+narrateur|Il reste assis.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>bol,chaise</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Alice va goûter. Que fait-elle ?</t>
+          <t>Amir va goûter. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1557,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Alice va goûter. Que fait-elle ?</t>
+          <t>narrateur|Amir va goûter.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Alice est assise. Les fesses sont sur la chaise. Maman et Alice mangent ensemble, à table.</t>
+          <t>Amir est assis. Il est à table. On est assis. On est ensemble. Le bol attend. Ta chaise reste à table ? Oui. Amir reste assis. Le rayon couché touche sa chaise. Tu restes avec moi ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1730,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Alice est assise. Les fesses sont sur la chaise. Maman et Alice mangent ensemble, à table.</t>
+          <t>narrateur|Amir est assis.
+narrateur|Il est à table.
+maman|On est assis.
+maman|On est ensemble.
+narrateur|Le bol attend.
+maman|Ta chaise reste à table ?
+enfant-m|Oui.
+narrateur|Amir reste assis.
+narrateur|Le rayon couché touche sa chaise.
+maman|Tu restes avec moi ?
+enfant-m|Oui.
+maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alice boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit maman.</t>
+          <t>Maman ouvre la boîte. Le biscuit sent le beurre. Tu croques le biscuit ? Amir croque le biscuit. C'est croustillant. C'est bon. Tu restes assis. Bravo, Amir. Tu as goûté. C'est du bon travail. Ils mangent ensemble. Amir reste assis. Encore un peu de cacao ? Encore une petite gorgée. Tu restes assis. Bravo. Merci, maman. Merci, Amir. Il boit une gorgée. Il reste assis jusqu'à la fin. Le rayon couché s'en va tout doucement.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1909,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Alice boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit maman.</t>
+          <t>narrateur|Maman ouvre la boîte.
+narrateur|Le biscuit sent le beurre.
+maman|Tu croques le biscuit ?
+narrateur|Amir croque le biscuit.
+enfant-m|C'est croustillant.
+enfant-m|C'est bon.
+maman|Tu restes assis.
+maman|Bravo, Amir.
+maman|Tu as goûté.
+maman|C'est du bon travail.
+narrateur|Ils mangent ensemble.
+narrateur|Amir reste assis.
+maman|Encore un peu de cacao ?
+narrateur|Encore une petite gorgée.
+maman|Tu restes assis. Bravo.
+enfant-m|Merci, maman.
+maman|Merci, Amir.
+narrateur|Il boit une gorgée.
+narrateur|Il reste assis jusqu'à la fin.
+narrateur|Le rayon couché s'en va tout doucement.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le cacao ne fume plus. La boîte est refermée. On a goûté assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2096,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le cacao ne fume plus.
+narrateur|La boîte est refermée.
+maman|On a goûté assis, ensemble.
+enfant-m|C'était bon.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est l'heure du goûter. Alice sent le cacao. Maman appelle. Alice va à la table. Elle pose les fesses sur la chaise. Elle est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e. Maman s'assoit près d'elle. Elles sont ensemble. Le bol est chaud. Alice mange assise. La cuillère cliquette. Maman dit : on mange ensemble, à table. Alice reste assise. Elle croque le biscuit. Il est croustillant. Maman sourit. Alice sourit aussi. Elles restent ensemble à table.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon couché s'étire sur le plancher. Il est long, tout doré. L'horloge fait tic, tic. Le salon est calme, derrière. Ça sent le cacao. Une petite fumée sort du bol. La boîte des biscuits est sur la table. Elle est ronde, un peu rouge. Amir vit ici, avec maman. Papa est au jardin, tout près. Une mouche tapote la vitre. Tic. Tic. Amir arrive du salon. Ses chaussettes glissent un peu. Elles sont rouges, tout douces. Maman, ça sent le chocolat ! Oui, Amir. C'est l'heure du goûter. Viens t'asseoir. Amir va vers sa chaise. Le bois du plancher est chaud. Tu as vu le rayon couché ? Il est long. Il tire un peu la chaise. Il s'assoit. Il pose les pieds par terre. Bravo, Amir. Tu es bien assis. Maman s'assoit près de lui. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Il pose les mains. Le bol est chaud. La cuillère cliquette. Tu as vu la petite fumée ? Elle fait des ronds. On attend un petit moment. Amir tient sa cuillère. Il reste assis.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Alice va goûter. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir va goûter. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1561,7 +1561,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1591,7 +1590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Alice est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e. Les fesses sont sur la chaise. Maman et Alice mangent ensemble, à table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est assis. Il est à table. On est assis. On est ensemble. Le bol attend. Ta chaise reste à table ? Oui. Amir reste assis. Le rayon couché touche sa chaise. Tu restes avec moi ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1744,7 +1743,6 @@
 maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1769,12 +1767,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman ouvre la boîte. Le biscuit sent le beurre. Tu croques le biscuit ? Amir croque le biscuit. C'est croustillant. C'est bon. Tu restes assis. Bravo, Amir. Tu as goûté. C'est du bon travail. Ils mangent ensemble. Amir reste assis. Encore un peu de cacao ? Encore une petite gorgée. Tu restes assis. Bravo. Merci, maman. Merci, Amir. Il boit une gorgée. Il reste assis jusqu'à la fin. Le rayon couché s'en va tout doucement.</t>
+          <t>Maman ouvre la boîte. Le biscuit sent le beurre. Tu croques le biscuit ? Amir croque le biscuit. C'est croustillant. C'est bon. Tu restes assis. Bravo, Amir. Tu as goûté. Ils mangent ensemble. Amir reste assis. Encore un peu de cacao ? Encore une petite gorgée. Tu restes assis. Bravo. Merci, maman. Merci, Amir. Il boit une gorgée. Il reste assis jusqu'à la fin. Le rayon couché s'en va tout doucement.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Alice boit une gorgée. Elle reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e jusqu'à la fin. Merci, dit maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman ouvre la boîte. Le biscuit sent le beurre. Tu croques le biscuit ? Amir croque le biscuit. C'est croustillant. C'est bon. Tu restes assis. Bravo, Amir. Tu as goûté. Ils mangent ensemble. Amir reste assis. Encore un peu de cacao ? Encore une petite gorgée. Tu restes assis. Bravo. Merci, maman. Merci, Amir. Il boit une gorgée. Il reste assis jusqu'à la fin. Le rayon couché s'en va tout doucement.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1918,7 +1916,6 @@
 maman|Tu restes assis.
 maman|Bravo, Amir.
 maman|Tu as goûté.
-maman|C'est du bon travail.
 narrateur|Ils mangent ensemble.
 narrateur|Amir reste assis.
 maman|Encore un peu de cacao ?
@@ -1931,7 +1928,6 @@
 narrateur|Le rayon couché s'en va tout doucement.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le cacao ne fume plus. La boîte est refermée. On a goûté assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>Le cacao ne fume plus. La boîte est refermée. On a goûté assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cacao ne fume plus. La boîte est refermée. On a goûté assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,12 +2096,9 @@
 narrateur|La boîte est refermée.
 maman|On a goûté assis, ensemble.
 enfant-m|C'était bon.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2124,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-06.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alice, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
